--- a/ru/downloads/data-excel/17.6.1.xlsx
+++ b/ru/downloads/data-excel/17.6.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="195" yWindow="600" windowWidth="28605" windowHeight="15600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
